--- a/demo/pq-odata.xlsx
+++ b/demo/pq-odata.xlsx
@@ -125,5 +125,5 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<DataMashup xmlns="http://schemas.microsoft.com/DataMashup">AAAAAC8DAABQSwMEFAAAAAgAwr71XH+/08qcAAAA5AAAABMAAABbQ29udGVudF9UeXBlc10ueG1sbY5LDsIwDESvEnmfurBACDXtArgBF4iC+xHNR42Lwu1J6A516Zl5nmm6ZGfxpiVO3ik4VDUIcsY/JzcoWLmXZ+ja5vEJFEWOuqhgZA4XxGhGsjpWPpDLTu8Xqzmfy4BBm5ceCI91fULjHZNjyeUHtM2Ner3OLO4py1ttxkFct1ypUsCUGIuMu4D9i+sQ5sloziYmaaO0BcTf7PYLUEsDBBQAAAAIAMK+9Vy5xFaLhwAAALsAAAASAAAAQ29uZmlnL1BhY2thZ2UueG1sTY3BCgIhFEV/RdyPb2oV8XQWtR0IovZiziiNOugz+vwGSmh3D9x7Dw7vsLCXzcWnKPlO9JzZaNLDx1nySlN34IPCizZPPVu2lWOR3BGtR4BinA26iOBNTiVNJEwKcNakR11cXeE34wrvX4Paix6hAY4+tryZEf4YT3Whmq2ysbtdERpiO1UfUEsDBBQAAAAIAMK+9VzHpvlSogAAAPgAAAATAAAARm9ybXVsYXMvU2VjdGlvbjEubV1NvQqDMBDe8xRHJgvW4ixOLV2lmBeIeqWWmJPkMoj47o3agvSW4/v32HJPFur954UQ/qUddlAFHgNDCQZZQLyagmsxEtVNs87uiF0iL9RFcPbaoM/enqw8pZtbTWMsKUHpxmCmnLb+SW64kgmDXUWf7IUpzLN8BG2550mmwFEDG4YG3RI1qYi1+eOX70hNjg8rK0y24a30l8yjX/T2kCjEB1BLAQIUABQAAAAIAMK+9Vx/v9PKnAAAAOQAAAATAAAAAAAAAAAAAAAAAAAAAABbQ29udGVudF9UeXBlc10ueG1sUEsBAhQAFAAAAAgAwr71XLnEVouHAAAAuwAAABIAAAAAAAAAAAAAAAAAzQAAAENvbmZpZy9QYWNrYWdlLnhtbFBLAQIUABQAAAAIAMK+9VzHpvlSogAAAPgAAAATAAAAAAAAAAAAAAAAAIQBAABGb3JtdWxhcy9TZWN0aW9uMS5tUEsFBgAAAAADAAMAwgAAAFcCAAAAANcAAAA8P3htbCB2ZXJzaW9uPSIxLjAiIGVuY29kaW5nPSJ1dGYtOCI/PjxQZXJtaXNzaW9uTGlzdCB4bWxuczp4c2Q9Imh0dHA6Ly93d3cudzMub3JnLzIwMDEvWE1MU2NoZW1hIj48Q2FuRXZhbHVhdGVGdXR1cmVQYWNrYWdlcz5mYWxzZTwvQ2FuRXZhbHVhdGVGdXR1cmVQYWNrYWdlcz48RmlyZXdhbGxFbmFibGVkPnRydWU8L0ZpcmV3YWxsRW5hYmxlZD48L1Blcm1pc3Npb25MaXN0PgAAAAAAAAAA</DataMashup>
+<DataMashup xmlns="http://schemas.microsoft.com/DataMashup">AAAAAC8DAABQSwMEFAAAAAgAeUD2XH+/08qcAAAA5AAAABMAAABbQ29udGVudF9UeXBlc10ueG1sbY5LDsIwDESvEnmfurBACDXtArgBF4iC+xHNR42Lwu1J6A516Zl5nmm6ZGfxpiVO3ik4VDUIcsY/JzcoWLmXZ+ja5vEJFEWOuqhgZA4XxGhGsjpWPpDLTu8Xqzmfy4BBm5ceCI91fULjHZNjyeUHtM2Ner3OLO4py1ttxkFct1ypUsCUGIuMu4D9i+sQ5sloziYmaaO0BcTf7PYLUEsDBBQAAAAIAHlA9ly5xFaLhwAAALsAAAASAAAAQ29uZmlnL1BhY2thZ2UueG1sTY3BCgIhFEV/RdyPb2oV8XQWtR0IovZiziiNOugz+vwGSmh3D9x7Dw7vsLCXzcWnKPlO9JzZaNLDx1nySlN34IPCizZPPVu2lWOR3BGtR4BinA26iOBNTiVNJEwKcNakR11cXeE34wrvX4Paix6hAY4+tryZEf4YT3Whmq2ysbtdERpiO1UfUEsDBBQAAAAIAHlA9lzHpvlSogAAAPgAAAATAAAARm9ybXVsYXMvU2VjdGlvbjEubV1NvQqDMBDe8xRHJgvW4ixOLV2lmBeIeqWWmJPkMoj47o3agvSW4/v32HJPFur954UQ/qUddlAFHgNDCQZZQLyagmsxEtVNs87uiF0iL9RFcPbaoM/enqw8pZtbTWMsKUHpxmCmnLb+SW64kgmDXUWf7IUpzLN8BG2550mmwFEDG4YG3RI1qYi1+eOX70hNjg8rK0y24a30l8yjX/T2kCjEB1BLAQIUABQAAAAIAHlA9lx/v9PKnAAAAOQAAAATAAAAAAAAAAAAAAAAAAAAAABbQ29udGVudF9UeXBlc10ueG1sUEsBAhQAFAAAAAgAeUD2XLnEVouHAAAAuwAAABIAAAAAAAAAAAAAAAAAzQAAAENvbmZpZy9QYWNrYWdlLnhtbFBLAQIUABQAAAAIAHlA9lzHpvlSogAAAPgAAAATAAAAAAAAAAAAAAAAAIQBAABGb3JtdWxhcy9TZWN0aW9uMS5tUEsFBgAAAAADAAMAwgAAAFcCAAAAANcAAAA8P3htbCB2ZXJzaW9uPSIxLjAiIGVuY29kaW5nPSJ1dGYtOCI/PjxQZXJtaXNzaW9uTGlzdCB4bWxuczp4c2Q9Imh0dHA6Ly93d3cudzMub3JnLzIwMDEvWE1MU2NoZW1hIj48Q2FuRXZhbHVhdGVGdXR1cmVQYWNrYWdlcz5mYWxzZTwvQ2FuRXZhbHVhdGVGdXR1cmVQYWNrYWdlcz48RmlyZXdhbGxFbmFibGVkPnRydWU8L0ZpcmV3YWxsRW5hYmxlZD48L1Blcm1pc3Npb25MaXN0PgAAAAAAAAAA</DataMashup>
 </file>